--- a/Mechanical/Connectors/Modular/Database/Mechanical_Connectors_Modular_GOST.xlsx
+++ b/Mechanical/Connectors/Modular/Database/Mechanical_Connectors_Modular_GOST.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Electronics\Mechanical\Connectors\Modular\Database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB269E0E-9FC2-4946-B8BB-39B5AF1937A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B7CF63-D542-446D-87A3-DB511F751098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3030" yWindow="3030" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="78">
   <si>
     <t>Item ID</t>
   </si>
@@ -246,13 +246,19 @@
     <t>11.7mm</t>
   </si>
   <si>
-    <t>Connector Modular RJ45 plug 8p8c vertical board unshielded</t>
-  </si>
-  <si>
     <t>Plug</t>
   </si>
   <si>
     <t>Cat5</t>
+  </si>
+  <si>
+    <t>https://media.metz-connect.com/files/171/Data_sheet_AJP92A8813.PDF</t>
+  </si>
+  <si>
+    <t>https://www.metz-connect.com/home/produits/u-contact/connecteurs-femelles-pour-ci-connecteur-m-le/rj45.87.fr.html?id=AJP92A8813</t>
+  </si>
+  <si>
+    <t>Connector Modular RJ45 plug cat5 8p8c vertical board</t>
   </si>
 </sst>
 </file>
@@ -304,10 +310,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -603,7 +610,7 @@
     <col min="16" max="16" width="7.42578125" style="1" customWidth="1"/>
     <col min="17" max="17" width="7.140625" style="1" customWidth="1"/>
     <col min="18" max="18" width="6.7109375" style="1" customWidth="1"/>
-    <col min="19" max="19" width="11.85546875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="7.85546875" style="1" customWidth="1"/>
     <col min="20" max="20" width="7" style="1" customWidth="1"/>
     <col min="21" max="21" width="4.5703125" style="1" customWidth="1"/>
     <col min="22" max="22" width="5.85546875" style="1" customWidth="1"/>
@@ -761,7 +768,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>52</v>
@@ -794,13 +801,13 @@
         <v>65</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>42</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q2" s="1" t="s">
         <v>43</v>
@@ -838,8 +845,12 @@
       <c r="AG2" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AH2" s="2"/>
-      <c r="AI2" s="2"/>
+      <c r="AH2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AI2" s="3" t="s">
+        <v>76</v>
+      </c>
       <c r="AJ2" s="1" t="s">
         <v>53</v>
       </c>
@@ -869,8 +880,10 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="AG2" r:id="rId1" xr:uid="{9289CAC4-4CD8-4591-BF0E-BBD2267D5B24}"/>
+    <hyperlink ref="AH2" r:id="rId2" xr:uid="{B4EC302E-C1D0-48CB-ACF2-E691151F5F0A}"/>
+    <hyperlink ref="AI2" r:id="rId3" xr:uid="{4D02CE1B-ACBB-4779-AEB2-A72D1379E1AC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
--- a/Mechanical/Connectors/Modular/Database/Mechanical_Connectors_Modular_GOST.xlsx
+++ b/Mechanical/Connectors/Modular/Database/Mechanical_Connectors_Modular_GOST.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Electronics\Mechanical\Connectors\Modular\Database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B7CF63-D542-446D-87A3-DB511F751098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{423525FA-3B4D-4C93-9D38-9FADDCE253A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3030" yWindow="3030" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="2" r:id="rId1"/>
@@ -258,7 +258,7 @@
     <t>https://www.metz-connect.com/home/produits/u-contact/connecteurs-femelles-pour-ci-connecteur-m-le/rj45.87.fr.html?id=AJP92A8813</t>
   </si>
   <si>
-    <t>Connector Modular RJ45 plug cat5 8p8c vertical board</t>
+    <t>Connector modular RJ45 plug cat5 8p8c vertical board</t>
   </si>
 </sst>
 </file>
